--- a/defence/Dataset_Guide.xlsx
+++ b/defence/Dataset_Guide.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Failure rates differ 38-fold between projects, so this is the single strongest predictor.</t>
+          <t>Failure rates run from 0.0% to 38.3% between projects (elevenfold across the seventeen that fail at all), so this is the single strongest predictor.</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>This 38-fold spread is why a model told only the repository name already predicts well.</t>
+          <t>This 0.0%-to-38.3% spread is why a model told only the repository name already predicts well.</t>
         </is>
       </c>
     </row>
